--- a/Design/Excel/ET/Datas/Product/CompanionConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/CompanionConfig.xlsx
@@ -939,267 +939,267 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <x:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="9" style="2" customWidth="0"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Post</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SpawnX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SpawnY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AskTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ClearTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WashTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="str">
-        <x:v>PreparationChat</x:v>
-      </x:c>
-      <x:c r="K1" t="str">
-        <x:v>CooperationChat</x:v>
-      </x:c>
-      <x:c r="L1" t="str">
-        <x:v>ClosingChat</x:v>
-      </x:c>
-      <x:c r="M1" t="str">
-        <x:v>WorkFeedback</x:v>
-      </x:c>
-      <x:c r="N1" t="str">
-        <x:v>GrowthFeedback</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="K2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="L2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Post</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SpawnX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SpawnY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AskTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ClearTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WashTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>准备态备菜聊天</x:v>
-      </x:c>
-      <x:c r="K3" t="str">
-        <x:v>准备态合作聊天</x:v>
-      </x:c>
-      <x:c r="L3" t="str">
-        <x:v>准备态收店聊天</x:v>
-      </x:c>
-      <x:c r="M3" t="str">
-        <x:v>真实伙伴完成反馈</x:v>
-      </x:c>
-      <x:c r="N3" t="str">
-        <x:v>本关第三次成长反馈</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>小麦</x:v>
-      </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">30</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">61</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J4" t="str">
-        <x:v>先理好食材，再开店就从容啦。</x:v>
-      </x:c>
-      <x:c r="K4" t="str">
-        <x:v>我来问单和洗碗，清桌就拜托你啦。</x:v>
-      </x:c>
-      <x:c r="L4" t="str">
-        <x:v>忙完把餐具收好，咱们再一起收店。</x:v>
-      </x:c>
-      <x:c r="M4" t="str">
-        <x:v>这边忙好啦！</x:v>
-      </x:c>
-      <x:c r="N4" t="str">
-        <x:v>越做越顺啦，这一关洗碗我会更快些！</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpawnX</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpawnY</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AskTicks</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClearTicks</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WashTicks</t>
+        </is>
+      </c>
+      <c r="J1" t="str">
+        <v>PreparationChat</v>
+      </c>
+      <c r="K1" t="str">
+        <v>CooperationChat</v>
+      </c>
+      <c r="L1" t="str">
+        <v>ClosingChat</v>
+      </c>
+      <c r="M1" t="str">
+        <v>WorkFeedback</v>
+      </c>
+      <c r="N1" t="str">
+        <v>GrowthFeedback</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CompanionPost</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="J2" t="str">
+        <v>string</v>
+      </c>
+      <c r="K2" t="str">
+        <v>string</v>
+      </c>
+      <c r="L2" t="str">
+        <v>string</v>
+      </c>
+      <c r="M2" t="str">
+        <v>string</v>
+      </c>
+      <c r="N2" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpawnX</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SpawnY</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AskTicks</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ClearTicks</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WashTicks</t>
+        </is>
+      </c>
+      <c r="J3" t="str">
+        <v>准备态备菜聊天</v>
+      </c>
+      <c r="K3" t="str">
+        <v>准备态合作聊天</v>
+      </c>
+      <c r="L3" t="str">
+        <v>准备态收店聊天</v>
+      </c>
+      <c r="M3" t="str">
+        <v>真实伙伴完成反馈</v>
+      </c>
+      <c r="N3" t="str">
+        <v>本关第三次成长反馈</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="str">
+        <v>小麦</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FrontService</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61</t>
+        </is>
+      </c>
+      <c r="J4" t="str">
+        <v>先理好食材，再开店就从容啦。</v>
+      </c>
+      <c r="K4" t="str">
+        <v>我来问单和洗碗，清桌就拜托你啦。</v>
+      </c>
+      <c r="L4" t="str">
+        <v>忙完把餐具收好，咱们再一起收店。</v>
+      </c>
+      <c r="M4" t="str">
+        <v>这边忙好啦！</v>
+      </c>
+      <c r="N4" t="str">
+        <v>越做越顺啦，这一关洗碗我会更快些！</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>